--- a/appointment_forms/049_critical_incident_response_session_appointment_form--appointment_forms.xlsx
+++ b/appointment_forms/049_critical_incident_response_session_appointment_form--appointment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'open',_'label':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Open', 'label': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress',_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress', 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'closed',_'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Closed', 'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'team',_'label':_'team'}</t>
+          <t>team</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Team', 'label': 'Team'}</t>
+          <t>Team</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'individual',_'label':_'individual'}</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Individual', 'label': 'Individual'}</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'both',_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Both', 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'natural_disaster',_'label':_'natural_disaster'}</t>
+          <t>natural_disaster</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Natural Disaster', 'label': 'Natural Disaster'}</t>
+          <t>Natural Disaster</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'man-made',_'label':_'man-made'}</t>
+          <t>man-made</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Man-made', 'label': 'Man-made'}</t>
+          <t>Man-made</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'both',_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Both', 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'virtual',_'label':_'virtual'}</t>
+          <t>virtual</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Virtual', 'label': 'Virtual'}</t>
+          <t>Virtual</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'in_person',_'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'In Person', 'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
